--- a/詳細設計/03_詳細設計書_書写規範.xlsx
+++ b/詳細設計/03_詳細設計書_書写規範.xlsx
@@ -1,33 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="00_表紙" sheetId="1" ns1:id="R8bffcfd6ec674eb1"/>
-    <sheet name="01_改訂履歴" sheetId="2" ns1:id="R7d346d9352af421b"/>
-    <sheet name="02_基本原則" sheetId="3" ns1:id="R19b170efe9184252"/>
-    <sheet name="03_記述ルール" sheetId="4" ns1:id="R66b9eb9c6be94847"/>
-    <sheet name="04_命名採番" sheetId="5" ns1:id="R3b25c2699cd64962"/>
-    <sheet name="05_図表ルール" sheetId="6" ns1:id="R8c0cbf53fd314c1f"/>
-    <sheet name="06_記載例" sheetId="7" ns1:id="R53d644a49ce94482"/>
-    <sheet name="07_禁止事項" sheetId="8" ns1:id="Rc81ef5f955254f58"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'00_表紙'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'01_改訂履歴'!$A$1:$H$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'02_基本原則'!$A$1:$E$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'02_基本原則'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'03_記述ルール'!$A$1:$E$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'03_記述ルール'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'04_命名採番'!$A$1:$E$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'04_命名採番'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'05_図表ルール'!$A$1:$E$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'05_図表ルール'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'06_記載例'!$A$1:$E$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'06_記載例'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'07_禁止事項'!$A$1:$E$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'07_禁止事項'!$1:$7</definedName>
-  </definedNames>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re7edd601f5aa41d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R10bf038d61e5473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_基本原則" sheetId="3" r:id="Rf14ff669072349b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_記述ルール" sheetId="4" r:id="R5189c55724e54cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_命名採番" sheetId="5" r:id="Rd72e2c601be14be7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_図表ルール" sheetId="6" r:id="R91e0293797e341d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_記載例" sheetId="7" r:id="R43f2af4755974849"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_禁止事項" sheetId="8" r:id="Rdc1f9d5156ab4847"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -235,7 +219,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="74">
+  <x:cellXfs count="76">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -450,6 +434,12 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -701,8 +691,7 @@
 企業従業員・タスク管理システム</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>Company WorkHub
-企業従業員・タスク管理システム</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>Company WorkHub
@@ -930,7 +919,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.5</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
         <x:v>Ver.1.0</x:v>
@@ -947,8 +936,8 @@
       <x:c r="D16" s="11" t="str">
         <x:v>作成日</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="n">
-        <x:v>46294</x:v>
+      <x:c r="E16" s="16" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="F16" s="16" t="n">
         <x:v>46240</x:v>
@@ -1327,7 +1316,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -1502,25 +1491,57 @@
       </x:c>
       <x:c r="I11" s="64"/>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="2"/>
-      <x:c r="B13" s="2"/>
-      <x:c r="C13" s="2"/>
-      <x:c r="D13" s="2"/>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="2"/>
-      <x:c r="H13" s="2"/>
+    <x:row r="12" ht="55" customHeight="1">
+      <x:c r="A12" s="74" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B12" s="74" t="str">
+        <x:v>Ver.1.4</x:v>
+      </x:c>
+      <x:c r="C12" s="75" t="n">
+        <x:v>46302</x:v>
+      </x:c>
+      <x:c r="D12" s="74" t="str">
+        <x:v>CHG-MIG-20261007-01：DB詳細設計ごとのFlyway Version帯、欠番、追加時の採番規則をWR-ID-010に明確化。</x:v>
+      </x:c>
+      <x:c r="E12" s="74" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F12" s="74" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G12" s="74" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="H12" s="74" t="str">
+        <x:v>修正済（承認前）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="68" customHeight="1">
+      <x:c r="A13" s="74" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B13" s="74" t="str">
+        <x:v>Ver.1.5</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D13" s="74" t="str">
+        <x:v>CHG-TRACE-20261008-01：DB関連APIの全件逆引き規則と、Baseline／Change ID／参照基準日の転記規則を明確化。</x:v>
+      </x:c>
+      <x:c r="E13" s="74" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F13" s="74" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G13" s="74" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="H13" s="74" t="str">
+        <x:v>修正済（承認前）</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="2"/>
@@ -1771,7 +1792,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -2461,7 +2482,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -2766,7 +2787,7 @@
         <x:v>01D／20</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="64" customHeight="1">
+    <x:row r="23" ht="96" customHeight="1">
       <x:c r="A23" s="73" t="str">
         <x:v>WR-TXT-016</x:v>
       </x:c>
@@ -2774,13 +2795,13 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="C23" s="73" t="str">
-        <x:v>DBは項目・制約・Index・DDL・初期データ・Migration・試験を一致させる。物理外鍵なしでも論理参照と検証責任を省略しない。</x:v>
+        <x:v>DBは項目・制約・Index・DDL・初期データ・Migration・試験を一致させる。物理外鍵なしでも論理参照と検証責任を省略しない。関連APIは10～14／22_API処理・権限の関連Tableに対象Table名が完全一致するAPI IDを全件・昇順で記載する。Redis／File等の非DB資源とAPI Group名は記載しない。</x:v>
       </x:c>
       <x:c r="D23" s="73" t="str">
         <x:v>CK-DB-001, CK-DB-002, CK-DB-003, CK-DB-012, CK-DB-013, CK-DB-014, CK-DB-015, CK-DB-016</x:v>
       </x:c>
       <x:c r="E23" s="73" t="str">
-        <x:v>01E／DB01</x:v>
+        <x:v>01E／DB01、10～14／22、00／05</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="52" customHeight="1">
@@ -3201,7 +3222,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -3412,13 +3433,13 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="C17" s="57" t="str">
-        <x:v>採番済IDは再利用しない。Migrationの撤回番号も再利用せず、欠番理由を履歴に残す。</x:v>
+        <x:v>採番済IDは再利用しない。Migrationの撤回番号も再利用せず、欠番理由を履歴に残す。Version帯はDB-DD-01=V101～V110、DB-DD-02=V201～V210、DB-DD-03=V301～V310とする。帯内の未使用番号は空SQLを作成せず、追加時は昇順で採番する。帯を超える追加はProject Leaderが新帯を割り当てる。</x:v>
       </x:c>
       <x:c r="D17" s="57" t="str">
         <x:v>CK-GEN-004; CK-DB-012</x:v>
       </x:c>
       <x:c r="E17" s="57" t="str">
-        <x:v>各履歴</x:v>
+        <x:v>DB-DD-01／02／03、各改訂履歴</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3871,7 +3892,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -4541,7 +4562,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -5201,7 +5222,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.3　改訂日：2026-09-29</x:v>
+        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>

--- a/詳細設計/03_詳細設計書_書写規範.xlsx
+++ b/詳細設計/03_詳細設計書_書写規範.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re7edd601f5aa41d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R10bf038d61e5473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_基本原則" sheetId="3" r:id="Rf14ff669072349b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_記述ルール" sheetId="4" r:id="R5189c55724e54cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_命名採番" sheetId="5" r:id="Rd72e2c601be14be7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_図表ルール" sheetId="6" r:id="R91e0293797e341d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_記載例" sheetId="7" r:id="R43f2af4755974849"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_禁止事項" sheetId="8" r:id="Rdc1f9d5156ab4847"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R08e332a600764d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rcbfcdb86cc974920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_基本原則" sheetId="3" r:id="R40951c7472bf493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_記述ルール" sheetId="4" r:id="Ra496d5ddae524af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_命名採番" sheetId="5" r:id="Rc73cc1134c98437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_図表ルール" sheetId="6" r:id="Rfdcc8bb3334e4845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_記載例" sheetId="7" r:id="R443610a7ac794e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_禁止事項" sheetId="8" r:id="Rf734dce11f074cc3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -919,7 +919,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>Ver.1.5</x:v>
+        <x:v>Ver.1.6</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
         <x:v>Ver.1.0</x:v>
@@ -936,8 +936,8 @@
       <x:c r="D16" s="11" t="str">
         <x:v>作成日</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      <x:c r="E16" s="16" t="str">
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="F16" s="16" t="n">
         <x:v>46240</x:v>
@@ -1316,7 +1316,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
+        <x:v>Ver.1.6　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="45"/>
@@ -1544,14 +1544,30 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="2"/>
-      <x:c r="B14" s="2"/>
-      <x:c r="C14" s="2"/>
-      <x:c r="D14" s="2"/>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
-      <x:c r="H14" s="2"/>
+      <x:c r="A14" s="74" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B14" s="74" t="str">
+        <x:v>Ver.1.6</x:v>
+      </x:c>
+      <x:c r="C14" s="75" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="D14" s="74" t="str">
+        <x:v>正本参照だけでなく適用規則を本文へ展開する書き方を明確化。</x:v>
+      </x:c>
+      <x:c r="E14" s="74" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F14" s="74" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G14" s="74" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H14" s="74" t="str">
+        <x:v>修正済／Review待ち</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="2"/>
@@ -1792,7 +1808,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
+        <x:v>Ver.1.6　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -1850,7 +1866,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="C8" s="55" t="str">
-        <x:v>基本設計を上流正本とし、詳細設計は実装手順へ展開する。業務・契約の変更は変更管理で承認を得る。</x:v>
+        <x:v>基本設計を上流正本とし、対象機能の実装に必要な値・条件・Rule・異常後状態を詳細設計本文へ具体的に展開する。各事項の根拠は基本設計File／Sheet／設計ID又はCell位置・Baselineで示す。業務・契約の変更は変更管理で承認を得る。</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
         <x:v>CK-GEN-002, CK-GEN-009</x:v>
@@ -2482,7 +2498,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
+        <x:v>Ver.1.6　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -3222,7 +3238,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
+        <x:v>Ver.1.6　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -3892,7 +3908,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
+        <x:v>Ver.1.6　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -4562,7 +4578,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
+        <x:v>Ver.1.6　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -5222,7 +5238,7 @@
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45" t="str">
-        <x:v>Ver.1.5　改訂日：2026-10-08</x:v>
+        <x:v>Ver.1.6　改訂日：2026-10-15</x:v>
       </x:c>
       <x:c r="D4" s="45"/>
       <x:c r="E4" s="46"/>
@@ -5416,7 +5432,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="C16" s="55" t="str">
-        <x:v>共通の業務RuleやMessage正文を各文書で再定義しない。個別例外は正本の根拠を参照する。</x:v>
+        <x:v>共通の業務Rule・Message正文を詳細設計で独自に変更・創作しない。対象機能に適用する確定Ruleは具体的な条件・結果として記載し、上流正本のFile／Sheet／設計ID又はCell位置を付す。</x:v>
       </x:c>
       <x:c r="D16" s="55" t="str">
         <x:v>CK-GEN-002, CK-GEN-003; CK-API-009</x:v>
